--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/IOWA_2016.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2016/IOWA_2016.xlsx
@@ -445,7 +445,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="6">
@@ -643,7 +643,7 @@
         <v>3</v>
       </c>
       <c r="D16">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="17">
@@ -697,7 +697,7 @@
         <v>3</v>
       </c>
       <c r="D19">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="20">
@@ -1039,7 +1039,7 @@
         <v>3</v>
       </c>
       <c r="D38">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="39">
@@ -1273,7 +1273,7 @@
         <v>29</v>
       </c>
       <c r="D51">
-        <v>0.009382076997735361</v>
+        <v>0.009382076997735359</v>
       </c>
     </row>
     <row r="52">
@@ -1291,7 +1291,7 @@
         <v>3</v>
       </c>
       <c r="D52">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="53">
@@ -1309,7 +1309,7 @@
         <v>3</v>
       </c>
       <c r="D53">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="54">
@@ -1399,7 +1399,7 @@
         <v>3</v>
       </c>
       <c r="D58">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="59">
@@ -1651,7 +1651,7 @@
         <v>3</v>
       </c>
       <c r="D72">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="73">
@@ -1687,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="D74">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="75">
@@ -2191,7 +2191,7 @@
         <v>3</v>
       </c>
       <c r="D102">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="103">
@@ -2281,7 +2281,7 @@
         <v>3</v>
       </c>
       <c r="D107">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="108">
@@ -2551,7 +2551,7 @@
         <v>3</v>
       </c>
       <c r="D122">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="123">
@@ -2587,7 +2587,7 @@
         <v>3</v>
       </c>
       <c r="D124">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="125">
@@ -2677,7 +2677,7 @@
         <v>3</v>
       </c>
       <c r="D129">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="130">
@@ -2875,7 +2875,7 @@
         <v>3</v>
       </c>
       <c r="D140">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="141">
@@ -2911,7 +2911,7 @@
         <v>3</v>
       </c>
       <c r="D142">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="143">
@@ -3019,7 +3019,7 @@
         <v>3</v>
       </c>
       <c r="D148">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="149">
@@ -3037,7 +3037,7 @@
         <v>3</v>
       </c>
       <c r="D149">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="150">
@@ -3325,7 +3325,7 @@
         <v>3</v>
       </c>
       <c r="D165">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="166">
@@ -3361,7 +3361,7 @@
         <v>3</v>
       </c>
       <c r="D167">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="168">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C171">
@@ -3541,7 +3541,7 @@
         <v>3</v>
       </c>
       <c r="D177">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="178">
@@ -3577,7 +3577,7 @@
         <v>3</v>
       </c>
       <c r="D179">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="180">
@@ -3703,7 +3703,7 @@
         <v>3</v>
       </c>
       <c r="D186">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="187">
@@ -3739,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="D188">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="189">
@@ -4279,7 +4279,7 @@
         <v>3</v>
       </c>
       <c r="D218">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="219">
@@ -4315,7 +4315,7 @@
         <v>3</v>
       </c>
       <c r="D220">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="221">
@@ -4333,7 +4333,7 @@
         <v>3</v>
       </c>
       <c r="D221">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="222">
@@ -4369,7 +4369,7 @@
         <v>3</v>
       </c>
       <c r="D223">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="224">
@@ -4513,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="D231">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="232">
@@ -4711,7 +4711,7 @@
         <v>3</v>
       </c>
       <c r="D242">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="243">
@@ -5179,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="D268">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="269">
@@ -5287,7 +5287,7 @@
         <v>3</v>
       </c>
       <c r="D274">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="275">
@@ -5341,7 +5341,7 @@
         <v>3</v>
       </c>
       <c r="D277">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="278">
@@ -5359,7 +5359,7 @@
         <v>3</v>
       </c>
       <c r="D278">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="279">
@@ -5683,7 +5683,7 @@
         <v>3</v>
       </c>
       <c r="D296">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="297">
@@ -6061,7 +6061,7 @@
         <v>3</v>
       </c>
       <c r="D317">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="318">
@@ -6133,7 +6133,7 @@
         <v>3</v>
       </c>
       <c r="D321">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="322">
@@ -6511,7 +6511,7 @@
         <v>3</v>
       </c>
       <c r="D342">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="343">
@@ -6601,7 +6601,7 @@
         <v>3</v>
       </c>
       <c r="D347">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="348">
@@ -6727,7 +6727,7 @@
         <v>3</v>
       </c>
       <c r="D354">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="355">
@@ -7177,7 +7177,7 @@
         <v>3</v>
       </c>
       <c r="D379">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="380">
@@ -7249,7 +7249,7 @@
         <v>3</v>
       </c>
       <c r="D383">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="384">
@@ -7339,7 +7339,7 @@
         <v>3</v>
       </c>
       <c r="D388">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="389">
@@ -7393,7 +7393,7 @@
         <v>3</v>
       </c>
       <c r="D391">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="392">
@@ -7411,7 +7411,7 @@
         <v>3</v>
       </c>
       <c r="D392">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="393">
@@ -7429,7 +7429,7 @@
         <v>3</v>
       </c>
       <c r="D393">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="394">
@@ -7573,7 +7573,7 @@
         <v>3</v>
       </c>
       <c r="D401">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="402">
@@ -7591,7 +7591,7 @@
         <v>3</v>
       </c>
       <c r="D402">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="403">
@@ -7681,7 +7681,7 @@
         <v>3</v>
       </c>
       <c r="D407">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="408">
@@ -7897,7 +7897,7 @@
         <v>3</v>
       </c>
       <c r="D419">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="420">
@@ -7969,7 +7969,7 @@
         <v>3</v>
       </c>
       <c r="D423">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="424">
@@ -8131,7 +8131,7 @@
         <v>3</v>
       </c>
       <c r="D432">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="433">
@@ -8149,7 +8149,7 @@
         <v>3</v>
       </c>
       <c r="D433">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="434">
@@ -8383,7 +8383,7 @@
         <v>3</v>
       </c>
       <c r="D446">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="447">
@@ -8437,7 +8437,7 @@
         <v>3</v>
       </c>
       <c r="D449">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="450">
@@ -8491,7 +8491,7 @@
         <v>3</v>
       </c>
       <c r="D452">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="453">
@@ -8790,7 +8790,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec -Distrito 08-</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C469">
@@ -8887,7 +8887,7 @@
         <v>3</v>
       </c>
       <c r="D474">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="475">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C479">
@@ -9265,7 +9265,7 @@
         <v>3</v>
       </c>
       <c r="D495">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="496">
@@ -9697,7 +9697,7 @@
         <v>3</v>
       </c>
       <c r="D519">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="520">
@@ -9967,7 +9967,7 @@
         <v>3</v>
       </c>
       <c r="D534">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="535">
@@ -10165,7 +10165,7 @@
         <v>3</v>
       </c>
       <c r="D545">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="546">
@@ -10327,7 +10327,7 @@
         <v>3</v>
       </c>
       <c r="D554">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="555">
@@ -10471,7 +10471,7 @@
         <v>3</v>
       </c>
       <c r="D562">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="563">
@@ -10561,7 +10561,7 @@
         <v>3</v>
       </c>
       <c r="D567">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="568">
@@ -10651,7 +10651,7 @@
         <v>3</v>
       </c>
       <c r="D572">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="573">
@@ -10813,7 +10813,7 @@
         <v>3</v>
       </c>
       <c r="D581">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="582">
@@ -11011,7 +11011,7 @@
         <v>3</v>
       </c>
       <c r="D592">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="593">
@@ -11389,7 +11389,7 @@
         <v>3</v>
       </c>
       <c r="D613">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="614">
@@ -11443,7 +11443,7 @@
         <v>3</v>
       </c>
       <c r="D616">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="617">
@@ -12199,7 +12199,7 @@
         <v>3</v>
       </c>
       <c r="D658">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="659">
@@ -12415,7 +12415,7 @@
         <v>3</v>
       </c>
       <c r="D670">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="671">
@@ -12523,7 +12523,7 @@
         <v>3</v>
       </c>
       <c r="D676">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="677">
@@ -12541,7 +12541,7 @@
         <v>3</v>
       </c>
       <c r="D677">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="678">
@@ -12577,7 +12577,7 @@
         <v>3</v>
       </c>
       <c r="D679">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="680">
@@ -12631,7 +12631,7 @@
         <v>3</v>
       </c>
       <c r="D682">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="683">
@@ -12757,7 +12757,7 @@
         <v>3</v>
       </c>
       <c r="D689">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="690">
@@ -12829,7 +12829,7 @@
         <v>3</v>
       </c>
       <c r="D693">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="694">
@@ -13657,7 +13657,7 @@
         <v>3</v>
       </c>
       <c r="D739">
-        <v>0.0009705596894208993</v>
+        <v>0.0009705596894208992</v>
       </c>
     </row>
     <row r="740">
